--- a/data/dataset_pirelli_.xlsx
+++ b/data/dataset_pirelli_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{865A0272-7A95-4483-849B-C3F5B19C3317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC2AE9B-635E-4ABC-8CB2-DFB686B541E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="plants" sheetId="1" r:id="rId1"/>
@@ -1209,8 +1209,9 @@
   <cols>
     <col min="1" max="1" width="8.6328125" customWidth="1"/>
     <col min="2" max="3" width="16.6328125" customWidth="1"/>
-    <col min="4" max="5" width="8.453125" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.25" customHeight="1">
@@ -1367,10 +1368,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="2">
-        <v>5280274</v>
+        <v>52.80274</v>
       </c>
       <c r="F8" s="2">
-        <v>-162992</v>
+        <v>-1.62992</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1"/>

--- a/data/dataset_pirelli_.xlsx
+++ b/data/dataset_pirelli_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC2AE9B-635E-4ABC-8CB2-DFB686B541E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DF3CD2D-054F-45E1-B2F0-5078D5B729DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="plants" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="227">
   <si>
     <t>id</t>
   </si>
@@ -632,12 +632,6 @@
     <t>Спрос -8%</t>
   </si>
   <si>
-    <t>demand_108</t>
-  </si>
-  <si>
-    <t>Спрос +8%</t>
-  </si>
-  <si>
     <t>demand_112</t>
   </si>
   <si>
@@ -714,6 +708,18 @@
   </si>
   <si>
     <t>par_48</t>
+  </si>
+  <si>
+    <t>1,05</t>
+  </si>
+  <si>
+    <t>demand_105</t>
+  </si>
+  <si>
+    <t>Спрос +5%</t>
+  </si>
+  <si>
+    <t>ы</t>
   </si>
 </sst>
 </file>
@@ -14122,10 +14128,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C8A1A9-46B7-9940-8C25-AF214C0F8856}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="14" t="s">
         <v>174</v>
       </c>
@@ -14151,7 +14157,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" s="15" t="s">
         <v>182</v>
       </c>
@@ -14177,12 +14183,12 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C3" s="15">
         <v>2</v>
@@ -14200,15 +14206,15 @@
         <v>1</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C4" s="15">
         <v>3</v>
@@ -14226,15 +14232,15 @@
         <v>1</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -14252,15 +14258,15 @@
         <v>1</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C6" s="15">
         <v>5</v>
@@ -14278,15 +14284,15 @@
         <v>1</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C7" s="15">
         <v>6</v>
@@ -14304,10 +14310,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="15" t="s">
         <v>185</v>
       </c>
@@ -14333,7 +14339,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:10">
       <c r="A9" s="15" t="s">
         <v>187</v>
       </c>
@@ -14359,7 +14365,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:10">
       <c r="A10" s="15" t="s">
         <v>190</v>
       </c>
@@ -14385,7 +14391,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:10">
       <c r="A11" s="15" t="s">
         <v>192</v>
       </c>
@@ -14411,7 +14417,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:10">
       <c r="A12" s="15" t="s">
         <v>195</v>
       </c>
@@ -14436,10 +14442,13 @@
       <c r="H12" s="15" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="J12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="15" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>193</v>
@@ -14450,8 +14459,8 @@
       <c r="D13" s="15">
         <v>36</v>
       </c>
-      <c r="E13" s="16">
-        <v>1.08</v>
+      <c r="E13" s="16" t="s">
+        <v>223</v>
       </c>
       <c r="F13" s="15">
         <v>1</v>
@@ -14460,12 +14469,12 @@
         <v>1</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>193</v>
@@ -14486,15 +14495,15 @@
         <v>1</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C15" s="15">
         <v>14</v>
@@ -14512,15 +14521,15 @@
         <v>1</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C16" s="15">
         <v>15</v>
@@ -14538,15 +14547,15 @@
         <v>1</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C17" s="15">
         <v>16</v>
@@ -14564,15 +14573,15 @@
         <v>1</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C18" s="15">
         <v>17</v>
@@ -14590,15 +14599,15 @@
         <v>1</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C19" s="15">
         <v>18</v>
@@ -14616,15 +14625,15 @@
         <v>1</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C20" s="15">
         <v>19</v>
@@ -14642,7 +14651,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/data/dataset_pirelli_.xlsx
+++ b/data/dataset_pirelli_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DF3CD2D-054F-45E1-B2F0-5078D5B729DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24FE5F3-47A7-4F8B-BEB6-CFF1D0303647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="225">
   <si>
     <t>id</t>
   </si>
@@ -710,16 +710,10 @@
     <t>par_48</t>
   </si>
   <si>
-    <t>1,05</t>
-  </si>
-  <si>
     <t>demand_105</t>
   </si>
   <si>
     <t>Спрос +5%</t>
-  </si>
-  <si>
-    <t>ы</t>
   </si>
 </sst>
 </file>
@@ -14128,10 +14122,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C8A1A9-46B7-9940-8C25-AF214C0F8856}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:8">
       <c r="A1" s="14" t="s">
         <v>174</v>
       </c>
@@ -14157,7 +14151,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:8">
       <c r="A2" s="15" t="s">
         <v>182</v>
       </c>
@@ -14183,7 +14177,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:8">
       <c r="A3" s="15" t="s">
         <v>218</v>
       </c>
@@ -14209,7 +14203,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:8">
       <c r="A4" s="15" t="s">
         <v>219</v>
       </c>
@@ -14235,7 +14229,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:8">
       <c r="A5" s="15" t="s">
         <v>220</v>
       </c>
@@ -14261,7 +14255,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:8">
       <c r="A6" s="15" t="s">
         <v>221</v>
       </c>
@@ -14287,7 +14281,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:8">
       <c r="A7" s="15" t="s">
         <v>222</v>
       </c>
@@ -14313,7 +14307,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:8">
       <c r="A8" s="15" t="s">
         <v>185</v>
       </c>
@@ -14339,7 +14333,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:8">
       <c r="A9" s="15" t="s">
         <v>187</v>
       </c>
@@ -14365,7 +14359,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:8">
       <c r="A10" s="15" t="s">
         <v>190</v>
       </c>
@@ -14391,7 +14385,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:8">
       <c r="A11" s="15" t="s">
         <v>192</v>
       </c>
@@ -14417,7 +14411,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:8">
       <c r="A12" s="15" t="s">
         <v>195</v>
       </c>
@@ -14442,13 +14436,10 @@
       <c r="H12" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="J12" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>193</v>
@@ -14459,8 +14450,8 @@
       <c r="D13" s="15">
         <v>36</v>
       </c>
-      <c r="E13" s="16" t="s">
-        <v>223</v>
+      <c r="E13" s="15">
+        <v>1.05</v>
       </c>
       <c r="F13" s="15">
         <v>1</v>
@@ -14469,10 +14460,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="15" t="s">
         <v>197</v>
       </c>
@@ -14498,7 +14489,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:8">
       <c r="A15" s="15" t="s">
         <v>206</v>
       </c>
@@ -14524,7 +14515,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:8">
       <c r="A16" s="15" t="s">
         <v>210</v>
       </c>

--- a/data/dataset_pirelli_.xlsx
+++ b/data/dataset_pirelli_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24FE5F3-47A7-4F8B-BEB6-CFF1D0303647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB97D12-1010-404C-92CF-26F2394D5293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="226">
   <si>
     <t>id</t>
   </si>
@@ -714,6 +714,9 @@
   </si>
   <si>
     <t>Спрос +5%</t>
+  </si>
+  <si>
+    <t>1.05</t>
   </si>
 </sst>
 </file>
@@ -14450,8 +14453,8 @@
       <c r="D13" s="15">
         <v>36</v>
       </c>
-      <c r="E13" s="15">
-        <v>1.05</v>
+      <c r="E13" s="16" t="s">
+        <v>225</v>
       </c>
       <c r="F13" s="15">
         <v>1</v>

--- a/data/dataset_pirelli_.xlsx
+++ b/data/dataset_pirelli_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB97D12-1010-404C-92CF-26F2394D5293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5785F4D-2331-495E-AEFD-394250337064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="225">
   <si>
     <t>id</t>
   </si>
@@ -714,9 +714,6 @@
   </si>
   <si>
     <t>Спрос +5%</t>
-  </si>
-  <si>
-    <t>1.05</t>
   </si>
 </sst>
 </file>
@@ -14453,8 +14450,8 @@
       <c r="D13" s="15">
         <v>36</v>
       </c>
-      <c r="E13" s="16" t="s">
-        <v>225</v>
+      <c r="E13" s="15">
+        <v>1.05</v>
       </c>
       <c r="F13" s="15">
         <v>1</v>
@@ -14479,7 +14476,7 @@
       <c r="D14" s="15">
         <v>36</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="15">
         <v>1.1200000000000001</v>
       </c>
       <c r="F14" s="15">
